--- a/docs/data/Payroll_Statutory_2025/Muhamad Akram Hakim bin Jamaludin.xlsx
+++ b/docs/data/Payroll_Statutory_2025/Muhamad Akram Hakim bin Jamaludin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haziq\Averroes Data Science\Company\Velarix Technology Sdn Bhd\HR\Payslip\Statutory 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC4C42A-A661-471B-BB6A-B7DF34C89B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70054547-A129-4E8A-86FF-441EA8009209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5EB6A495-7700-48CF-A1E5-B50AF94CB8C1}"/>
   </bookViews>
@@ -296,71 +296,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -669,847 +669,847 @@
   <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="8.88671875" style="8"/>
-    <col min="4" max="4" width="11.44140625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="8"/>
-    <col min="8" max="8" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.88671875" style="8"/>
-    <col min="12" max="12" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="8.88671875" style="8"/>
-    <col min="16" max="16" width="13.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="8"/>
+    <col min="1" max="3" width="8.88671875" style="5"/>
+    <col min="4" max="4" width="11.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="5"/>
+    <col min="8" max="8" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.88671875" style="5"/>
+    <col min="12" max="12" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="8.88671875" style="5"/>
+    <col min="16" max="16" width="13.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1" t="s">
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5" t="s">
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+    </row>
+    <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="3">
         <v>2025</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>7000</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="3">
         <f>C3-SUM(E3:H3)</f>
         <v>5864.15</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="4">
         <v>770</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="4">
         <v>29.75</v>
       </c>
-      <c r="G3" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="G3" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H3" s="4">
         <v>324.2</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="4">
         <f>SUM(I2,E3)</f>
         <v>770</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="4">
         <f t="shared" ref="J3:L13" si="0">SUM(J2,F3)</f>
         <v>29.75</v>
       </c>
-      <c r="K3" s="7">
-        <f t="shared" si="0"/>
-        <v>11.9</v>
-      </c>
-      <c r="L3" s="7">
+      <c r="K3" s="4">
+        <f t="shared" si="0"/>
+        <v>11.9</v>
+      </c>
+      <c r="L3" s="4">
         <f t="shared" si="0"/>
         <v>324.2</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="4">
         <v>840</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="4">
         <v>104.15</v>
       </c>
-      <c r="O3" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P3" s="7">
+      <c r="O3" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P3" s="4">
         <f t="shared" ref="P3:R13" si="1">SUM(P2,M3)</f>
         <v>840</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="4">
         <f t="shared" si="1"/>
         <v>104.15</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R3" s="4">
         <f t="shared" si="1"/>
         <v>11.9</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>2025</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>7000</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <f t="shared" ref="D4:D13" si="2">C4-SUM(E4:H4)</f>
         <v>5864.15</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="4">
         <v>770</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="4">
         <v>29.75</v>
       </c>
-      <c r="G4" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H4" s="7">
+      <c r="G4" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H4" s="4">
         <v>324.2</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="4">
         <f>SUM(I3,E4)</f>
         <v>1540</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="4">
         <f t="shared" si="0"/>
         <v>59.5</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="4">
         <f t="shared" si="0"/>
         <v>23.8</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="4">
         <f t="shared" si="0"/>
         <v>648.4</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="4">
         <v>840</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="4">
         <v>104.15</v>
       </c>
-      <c r="O4" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P4" s="7">
+      <c r="O4" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P4" s="4">
         <f t="shared" si="1"/>
         <v>1680</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="4">
         <f t="shared" si="1"/>
         <v>208.3</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="4">
         <f t="shared" si="1"/>
         <v>23.8</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>2025</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <v>7000</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="3">
+        <f t="shared" si="2"/>
+        <v>5864.2</v>
+      </c>
+      <c r="E5" s="4">
+        <v>770</v>
+      </c>
+      <c r="F5" s="4">
+        <v>29.75</v>
+      </c>
+      <c r="G5" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H5" s="4">
+        <v>324.14999999999998</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" ref="I5:I13" si="3">SUM(I4,E5)</f>
+        <v>2310</v>
+      </c>
+      <c r="J5" s="4">
+        <f t="shared" si="0"/>
+        <v>89.25</v>
+      </c>
+      <c r="K5" s="4">
+        <f t="shared" si="0"/>
+        <v>35.700000000000003</v>
+      </c>
+      <c r="L5" s="4">
+        <f t="shared" si="0"/>
+        <v>972.55</v>
+      </c>
+      <c r="M5" s="4">
+        <v>840</v>
+      </c>
+      <c r="N5" s="4">
+        <v>104.15</v>
+      </c>
+      <c r="O5" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P5" s="4">
+        <f t="shared" si="1"/>
+        <v>2520</v>
+      </c>
+      <c r="Q5" s="4">
+        <f t="shared" si="1"/>
+        <v>312.45000000000005</v>
+      </c>
+      <c r="R5" s="4">
+        <f t="shared" si="1"/>
+        <v>35.700000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3">
+        <v>7000</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="2"/>
+        <v>5864.2</v>
+      </c>
+      <c r="E6" s="4">
+        <v>770</v>
+      </c>
+      <c r="F6" s="4">
+        <v>29.75</v>
+      </c>
+      <c r="G6" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H6" s="4">
+        <v>324.14999999999998</v>
+      </c>
+      <c r="I6" s="4">
+        <f t="shared" si="3"/>
+        <v>3080</v>
+      </c>
+      <c r="J6" s="4">
+        <f t="shared" si="0"/>
+        <v>119</v>
+      </c>
+      <c r="K6" s="4">
+        <f t="shared" si="0"/>
+        <v>47.6</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" si="0"/>
+        <v>1296.6999999999998</v>
+      </c>
+      <c r="M6" s="4">
+        <v>840</v>
+      </c>
+      <c r="N6" s="4">
+        <v>104.15</v>
+      </c>
+      <c r="O6" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" si="1"/>
+        <v>3360</v>
+      </c>
+      <c r="Q6" s="4">
+        <f t="shared" si="1"/>
+        <v>416.6</v>
+      </c>
+      <c r="R6" s="4">
+        <f t="shared" si="1"/>
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7000</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="2"/>
+        <v>5864.2</v>
+      </c>
+      <c r="E7" s="4">
+        <v>770</v>
+      </c>
+      <c r="F7" s="4">
+        <v>29.75</v>
+      </c>
+      <c r="G7" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H7" s="4">
+        <v>324.14999999999998</v>
+      </c>
+      <c r="I7" s="4">
+        <f t="shared" si="3"/>
+        <v>3850</v>
+      </c>
+      <c r="J7" s="4">
+        <f t="shared" si="0"/>
+        <v>148.75</v>
+      </c>
+      <c r="K7" s="4">
+        <f t="shared" si="0"/>
+        <v>59.5</v>
+      </c>
+      <c r="L7" s="4">
+        <f t="shared" si="0"/>
+        <v>1620.85</v>
+      </c>
+      <c r="M7" s="4">
+        <v>840</v>
+      </c>
+      <c r="N7" s="4">
+        <v>104.15</v>
+      </c>
+      <c r="O7" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="1"/>
+        <v>4200</v>
+      </c>
+      <c r="Q7" s="4">
+        <f t="shared" si="1"/>
+        <v>520.75</v>
+      </c>
+      <c r="R7" s="4">
+        <f t="shared" si="1"/>
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3">
+        <v>7000</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="2"/>
+        <v>5864.2</v>
+      </c>
+      <c r="E8" s="4">
+        <v>770</v>
+      </c>
+      <c r="F8" s="4">
+        <v>29.75</v>
+      </c>
+      <c r="G8" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H8" s="4">
+        <v>324.14999999999998</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="3"/>
+        <v>4620</v>
+      </c>
+      <c r="J8" s="4">
+        <f t="shared" si="0"/>
+        <v>178.5</v>
+      </c>
+      <c r="K8" s="4">
+        <f t="shared" si="0"/>
+        <v>71.400000000000006</v>
+      </c>
+      <c r="L8" s="4">
+        <f t="shared" si="0"/>
+        <v>1945</v>
+      </c>
+      <c r="M8" s="4">
+        <v>840</v>
+      </c>
+      <c r="N8" s="4">
+        <v>104.15</v>
+      </c>
+      <c r="O8" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" si="1"/>
+        <v>5040</v>
+      </c>
+      <c r="Q8" s="4">
+        <f t="shared" si="1"/>
+        <v>624.9</v>
+      </c>
+      <c r="R8" s="4">
+        <f t="shared" si="1"/>
+        <v>71.400000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3">
+        <v>7000</v>
+      </c>
+      <c r="D9" s="3">
         <f t="shared" si="2"/>
         <v>5864.15</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E9" s="4">
         <v>770</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F9" s="4">
         <v>29.75</v>
       </c>
-      <c r="G5" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G9" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H9" s="4">
         <v>324.2</v>
       </c>
-      <c r="I5" s="7">
-        <f t="shared" ref="I5:I13" si="3">SUM(I4,E5)</f>
-        <v>2310</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="0"/>
-        <v>89.25</v>
-      </c>
-      <c r="K5" s="7">
-        <f t="shared" si="0"/>
-        <v>35.700000000000003</v>
-      </c>
-      <c r="L5" s="7">
-        <f t="shared" si="0"/>
-        <v>972.59999999999991</v>
-      </c>
-      <c r="M5" s="7">
-        <v>840</v>
-      </c>
-      <c r="N5" s="7">
-        <v>104.15</v>
-      </c>
-      <c r="O5" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P5" s="7">
-        <f t="shared" si="1"/>
-        <v>2520</v>
-      </c>
-      <c r="Q5" s="7">
-        <f t="shared" si="1"/>
-        <v>312.45000000000005</v>
-      </c>
-      <c r="R5" s="7">
-        <f t="shared" si="1"/>
-        <v>35.700000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="6">
-        <v>7000</v>
-      </c>
-      <c r="D6" s="6">
-        <f t="shared" si="2"/>
-        <v>5864.15</v>
-      </c>
-      <c r="E6" s="7">
-        <v>770</v>
-      </c>
-      <c r="F6" s="7">
-        <v>29.75</v>
-      </c>
-      <c r="G6" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H6" s="7">
-        <v>324.2</v>
-      </c>
-      <c r="I6" s="7">
-        <f t="shared" si="3"/>
-        <v>3080</v>
-      </c>
-      <c r="J6" s="7">
-        <f t="shared" si="0"/>
-        <v>119</v>
-      </c>
-      <c r="K6" s="7">
-        <f t="shared" si="0"/>
-        <v>47.6</v>
-      </c>
-      <c r="L6" s="7">
-        <f t="shared" si="0"/>
-        <v>1296.8</v>
-      </c>
-      <c r="M6" s="7">
-        <v>840</v>
-      </c>
-      <c r="N6" s="7">
-        <v>104.15</v>
-      </c>
-      <c r="O6" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P6" s="7">
-        <f t="shared" si="1"/>
-        <v>3360</v>
-      </c>
-      <c r="Q6" s="7">
-        <f t="shared" si="1"/>
-        <v>416.6</v>
-      </c>
-      <c r="R6" s="7">
-        <f t="shared" si="1"/>
-        <v>47.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="6">
-        <v>7000</v>
-      </c>
-      <c r="D7" s="6">
-        <f t="shared" si="2"/>
-        <v>5864.15</v>
-      </c>
-      <c r="E7" s="7">
-        <v>770</v>
-      </c>
-      <c r="F7" s="7">
-        <v>29.75</v>
-      </c>
-      <c r="G7" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H7" s="7">
-        <v>324.2</v>
-      </c>
-      <c r="I7" s="7">
-        <f t="shared" si="3"/>
-        <v>3850</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" si="0"/>
-        <v>148.75</v>
-      </c>
-      <c r="K7" s="7">
-        <f t="shared" si="0"/>
-        <v>59.5</v>
-      </c>
-      <c r="L7" s="7">
-        <f t="shared" si="0"/>
-        <v>1621</v>
-      </c>
-      <c r="M7" s="7">
-        <v>840</v>
-      </c>
-      <c r="N7" s="7">
-        <v>104.15</v>
-      </c>
-      <c r="O7" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P7" s="7">
-        <f t="shared" si="1"/>
-        <v>4200</v>
-      </c>
-      <c r="Q7" s="7">
-        <f t="shared" si="1"/>
-        <v>520.75</v>
-      </c>
-      <c r="R7" s="7">
-        <f t="shared" si="1"/>
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="6">
-        <v>7000</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" si="2"/>
-        <v>5864.15</v>
-      </c>
-      <c r="E8" s="7">
-        <v>770</v>
-      </c>
-      <c r="F8" s="7">
-        <v>29.75</v>
-      </c>
-      <c r="G8" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H8" s="7">
-        <v>324.2</v>
-      </c>
-      <c r="I8" s="7">
-        <f t="shared" si="3"/>
-        <v>4620</v>
-      </c>
-      <c r="J8" s="7">
-        <f t="shared" si="0"/>
-        <v>178.5</v>
-      </c>
-      <c r="K8" s="7">
-        <f t="shared" si="0"/>
-        <v>71.400000000000006</v>
-      </c>
-      <c r="L8" s="7">
-        <f t="shared" si="0"/>
-        <v>1945.2</v>
-      </c>
-      <c r="M8" s="7">
-        <v>840</v>
-      </c>
-      <c r="N8" s="7">
-        <v>104.15</v>
-      </c>
-      <c r="O8" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P8" s="7">
-        <f t="shared" si="1"/>
-        <v>5040</v>
-      </c>
-      <c r="Q8" s="7">
-        <f t="shared" si="1"/>
-        <v>624.9</v>
-      </c>
-      <c r="R8" s="7">
-        <f t="shared" si="1"/>
-        <v>71.400000000000006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>2025</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="6">
-        <v>7000</v>
-      </c>
-      <c r="D9" s="6">
-        <f t="shared" si="2"/>
-        <v>5864.15</v>
-      </c>
-      <c r="E9" s="7">
-        <v>770</v>
-      </c>
-      <c r="F9" s="7">
-        <v>29.75</v>
-      </c>
-      <c r="G9" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H9" s="7">
-        <v>324.2</v>
-      </c>
-      <c r="I9" s="7">
+      <c r="I9" s="4">
         <f t="shared" si="3"/>
         <v>5390</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="4">
         <f t="shared" si="0"/>
         <v>208.25</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="4">
         <f t="shared" si="0"/>
         <v>83.300000000000011</v>
       </c>
-      <c r="L9" s="7">
-        <f t="shared" si="0"/>
-        <v>2269.4</v>
-      </c>
-      <c r="M9" s="7">
+      <c r="L9" s="4">
+        <f t="shared" si="0"/>
+        <v>2269.1999999999998</v>
+      </c>
+      <c r="M9" s="4">
         <v>840</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="4">
         <v>104.15</v>
       </c>
-      <c r="O9" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P9" s="7">
+      <c r="O9" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P9" s="4">
         <f t="shared" si="1"/>
         <v>5880</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="Q9" s="4">
         <f t="shared" si="1"/>
         <v>729.05</v>
       </c>
-      <c r="R9" s="7">
+      <c r="R9" s="4">
         <f t="shared" si="1"/>
         <v>83.300000000000011</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="3">
         <v>2025</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
         <v>7000</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <f t="shared" si="2"/>
-        <v>5864.15</v>
-      </c>
-      <c r="E10" s="7">
+        <v>5864.2</v>
+      </c>
+      <c r="E10" s="4">
         <v>770</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="4">
         <v>29.75</v>
       </c>
-      <c r="G10" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H10" s="7">
-        <v>324.2</v>
-      </c>
-      <c r="I10" s="7">
+      <c r="G10" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H10" s="4">
+        <v>324.14999999999998</v>
+      </c>
+      <c r="I10" s="4">
         <f t="shared" si="3"/>
         <v>6160</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="4">
         <f t="shared" si="0"/>
         <v>238</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="4">
         <f t="shared" si="0"/>
         <v>95.200000000000017</v>
       </c>
-      <c r="L10" s="7">
-        <f t="shared" si="0"/>
-        <v>2593.6</v>
-      </c>
-      <c r="M10" s="7">
+      <c r="L10" s="4">
+        <f t="shared" si="0"/>
+        <v>2593.35</v>
+      </c>
+      <c r="M10" s="4">
         <v>840</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="4">
         <v>104.15</v>
       </c>
-      <c r="O10" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P10" s="7">
+      <c r="O10" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P10" s="4">
         <f t="shared" si="1"/>
         <v>6720</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q10" s="4">
         <f t="shared" si="1"/>
         <v>833.19999999999993</v>
       </c>
-      <c r="R10" s="7">
+      <c r="R10" s="4">
         <f t="shared" si="1"/>
         <v>95.200000000000017</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="3">
         <v>2025</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="3">
         <v>7000</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="3">
         <f t="shared" si="2"/>
-        <v>5864.15</v>
-      </c>
-      <c r="E11" s="7">
+        <v>5864.2</v>
+      </c>
+      <c r="E11" s="4">
         <v>770</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="4">
         <v>29.75</v>
       </c>
-      <c r="G11" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H11" s="7">
-        <v>324.2</v>
-      </c>
-      <c r="I11" s="7">
+      <c r="G11" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H11" s="4">
+        <v>324.14999999999998</v>
+      </c>
+      <c r="I11" s="4">
         <f t="shared" si="3"/>
         <v>6930</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="4">
         <f t="shared" si="0"/>
         <v>267.75</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="4">
         <f t="shared" si="0"/>
         <v>107.10000000000002</v>
       </c>
-      <c r="L11" s="7">
-        <f t="shared" si="0"/>
-        <v>2917.7999999999997</v>
-      </c>
-      <c r="M11" s="7">
+      <c r="L11" s="4">
+        <f t="shared" si="0"/>
+        <v>2917.5</v>
+      </c>
+      <c r="M11" s="4">
         <v>840</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="4">
         <v>104.15</v>
       </c>
-      <c r="O11" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P11" s="7">
+      <c r="O11" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P11" s="4">
         <f t="shared" si="1"/>
         <v>7560</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="4">
         <f t="shared" si="1"/>
         <v>937.34999999999991</v>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="4">
         <f t="shared" si="1"/>
         <v>107.10000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="3">
         <v>2025</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="3">
         <v>7000</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="3">
         <f t="shared" si="2"/>
-        <v>5864.15</v>
-      </c>
-      <c r="E12" s="7">
+        <v>5864.2</v>
+      </c>
+      <c r="E12" s="4">
         <v>770</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="4">
         <v>29.75</v>
       </c>
-      <c r="G12" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H12" s="7">
-        <v>324.2</v>
-      </c>
-      <c r="I12" s="7">
+      <c r="G12" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H12" s="4">
+        <v>324.14999999999998</v>
+      </c>
+      <c r="I12" s="4">
         <f t="shared" si="3"/>
         <v>7700</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="4">
         <f t="shared" si="0"/>
         <v>297.5</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="4">
         <f t="shared" si="0"/>
         <v>119.00000000000003</v>
       </c>
-      <c r="L12" s="7">
-        <f t="shared" si="0"/>
-        <v>3241.9999999999995</v>
-      </c>
-      <c r="M12" s="7">
+      <c r="L12" s="4">
+        <f t="shared" si="0"/>
+        <v>3241.65</v>
+      </c>
+      <c r="M12" s="4">
         <v>840</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="4">
         <v>104.15</v>
       </c>
-      <c r="O12" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P12" s="7">
+      <c r="O12" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P12" s="4">
         <f t="shared" si="1"/>
         <v>8400</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="Q12" s="4">
         <f t="shared" si="1"/>
         <v>1041.5</v>
       </c>
-      <c r="R12" s="7">
+      <c r="R12" s="4">
         <f t="shared" si="1"/>
         <v>119.00000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+      <c r="A13" s="6">
         <v>2025</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="3">
         <v>8000</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="3">
         <f t="shared" si="2"/>
         <v>6564.2</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="4">
         <v>880</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <v>29.75</v>
       </c>
-      <c r="G13" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="H13" s="12">
+      <c r="G13" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="H13" s="9">
         <v>514.15</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="4">
         <f t="shared" si="3"/>
         <v>8580</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="4">
         <f t="shared" si="0"/>
         <v>327.25</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="4">
         <f t="shared" si="0"/>
         <v>130.90000000000003</v>
       </c>
-      <c r="L13" s="7">
-        <f t="shared" si="0"/>
-        <v>3756.1499999999996</v>
-      </c>
-      <c r="M13" s="13">
+      <c r="L13" s="4">
+        <f t="shared" si="0"/>
+        <v>3755.8</v>
+      </c>
+      <c r="M13" s="10">
         <v>960</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N13" s="4">
         <v>104.15</v>
       </c>
-      <c r="O13" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="P13" s="7">
+      <c r="O13" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="P13" s="4">
         <f t="shared" si="1"/>
         <v>9360</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="Q13" s="4">
         <f t="shared" si="1"/>
         <v>1145.6500000000001</v>
       </c>
-      <c r="R13" s="7">
+      <c r="R13" s="4">
         <f t="shared" si="1"/>
         <v>130.90000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16">
+      <c r="B14" s="18"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11">
         <f>SUM(D3:D13)</f>
-        <v>65205.700000000004</v>
-      </c>
-      <c r="E14" s="16">
+        <v>65206.049999999988</v>
+      </c>
+      <c r="E14" s="11">
         <f>SUM(E3:E13)</f>
         <v>8580</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="12">
         <f>SUM(F3:F13)</f>
         <v>327.25</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="13">
         <f>SUM(G3:G13)</f>
         <v>130.90000000000003</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="13">
         <f>SUM(H3:H13)</f>
-        <v>3756.1499999999996</v>
+        <v>3755.8</v>
       </c>
       <c r="I14" s="19"/>
       <c r="J14" s="20"/>
       <c r="K14" s="20"/>
       <c r="L14" s="21"/>
-      <c r="M14" s="18">
+      <c r="M14" s="13">
         <f>SUM(M3:M13)</f>
         <v>9360</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N14" s="13">
         <f>SUM(N3:N13)</f>
         <v>1145.6500000000001</v>
       </c>
-      <c r="O14" s="18">
+      <c r="O14" s="13">
         <f>SUM(O3:O13)</f>
         <v>130.90000000000003</v>
       </c>
@@ -1518,61 +1518,61 @@
       <c r="R14" s="21"/>
     </row>
     <row r="18" spans="9:15" x14ac:dyDescent="0.25">
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
     </row>
     <row r="19" spans="9:15" x14ac:dyDescent="0.25">
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
     </row>
     <row r="20" spans="9:15" x14ac:dyDescent="0.25">
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
     </row>
     <row r="21" spans="9:15" x14ac:dyDescent="0.25">
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
     </row>
     <row r="22" spans="9:15" x14ac:dyDescent="0.25">
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
     </row>
     <row r="23" spans="9:15" x14ac:dyDescent="0.25">
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
     </row>
     <row r="24" spans="9:15" x14ac:dyDescent="0.25">
-      <c r="O24" s="23"/>
+      <c r="O24" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="11">
